--- a/attribute_list/attribute_list_deprecated.xlsx
+++ b/attribute_list/attribute_list_deprecated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RiderProjects\ShapeofDreamsMod\attribute_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E68E236-1C52-4E34-95AC-AF8EAB60AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65377B70-02FB-4B54-AA7D-A44A356587B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="129">
   <si>
     <t>中文参数名</t>
   </si>
@@ -466,12 +466,16 @@
     <t>默认商品数量有3列=6个,修改shopAddedItems参数增加商店商品列数(所有Star_开头的类为天赋树类,未点出对应天赋不会生效)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>此文件已过时,请移步MD文件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +512,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -529,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -543,6 +556,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
@@ -830,130 +846,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
+      <c r="A1" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4">
         <v>2</v>
       </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>18</v>
+      <c r="A6" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
+      <c r="D7">
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
@@ -962,15 +950,15 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -979,15 +967,15 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -996,15 +984,15 @@
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
@@ -1013,15 +1001,15 @@
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
@@ -1030,15 +1018,15 @@
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
@@ -1047,15 +1035,15 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -1064,15 +1052,15 @@
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -1081,15 +1069,15 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -1098,15 +1086,15 @@
         <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -1115,15 +1103,15 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
@@ -1132,15 +1120,15 @@
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
@@ -1149,15 +1137,15 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1166,15 +1154,15 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -1183,15 +1171,15 @@
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
@@ -1200,15 +1188,15 @@
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1217,15 +1205,15 @@
         <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -1234,15 +1222,15 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -1251,15 +1239,15 @@
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
@@ -1268,15 +1256,15 @@
         <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
@@ -1285,15 +1273,15 @@
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -1302,197 +1290,251 @@
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
         <v>89</v>
       </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="370.5">
-      <c r="A32" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
       <c r="D32" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>100</v>
+      <c r="E32" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="370.5">
+      <c r="A35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
         <v>101</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B36" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C36" t="s">
         <v>7</v>
       </c>
-      <c r="D33">
+      <c r="D36">
         <v>4</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E36" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="1" customFormat="1" ht="99.75">
-      <c r="A34" s="6" t="s">
+    <row r="37" spans="1:5" s="1" customFormat="1" ht="99.75">
+      <c r="A37" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D37" s="6">
         <v>2</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" ht="28.5">
-      <c r="A35" s="6" t="s">
+    <row r="38" spans="1:5" s="1" customFormat="1" ht="28.5">
+      <c r="A38" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B38" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D38" s="6">
         <v>2</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="57">
-      <c r="A36" t="s">
+    <row r="39" spans="1:5" ht="57">
+      <c r="A39" t="s">
         <v>104</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B39" t="s">
         <v>105</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C39" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="114">
-      <c r="A37" t="s">
+    <row r="40" spans="1:5" ht="114">
+      <c r="A40" t="s">
         <v>112</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B40" t="s">
         <v>113</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C40" t="s">
         <v>114</v>
       </c>
-      <c r="D37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="4" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C41" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="4" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E3"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
